--- a/evals/results/sample_견적서.xlsx
+++ b/evals/results/sample_견적서.xlsx
@@ -26,7 +26,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'단가대비표'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'단가대비표'!$A$1:$H$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'산출근거'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'산출근거'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'산출근거'!$A$1:$D$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3469,7 +3469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3805,15 +3805,13 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>공구손료 및 경장비 기준액 (원)</t>
-        </is>
-      </c>
-      <c r="B19" s="26" t="n">
-        <v>4922974</v>
-      </c>
+          <t>레미콘(콘크리트) 재료비 1㎥당 (㎥)</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="n"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>노무비 계 4,922,974원 × 5%</t>
+          <t>제외 · 관급자재(발주처 지급) — 시공사 일위대가에서 제외</t>
         </is>
       </c>
       <c r="D19" s="14" t="inlineStr">
@@ -3825,7 +3823,7 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>잔여 콘크리트 재료비 기준액 (원)</t>
+          <t>공구손료 및 경장비 기준액 (원)</t>
         </is>
       </c>
       <c r="B20" s="26" t="n">
@@ -3845,55 +3843,75 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>적용 기준</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr"/>
-      <c r="C21" s="14" t="inlineStr"/>
-      <c r="D21" s="14" t="inlineStr"/>
+          <t>잔여 콘크리트 재료비 기준액 (원)</t>
+        </is>
+      </c>
+      <c r="B21" s="26" t="n">
+        <v>4922974</v>
+      </c>
+      <c r="C21" s="14" t="inlineStr">
+        <is>
+          <t>노무비 계 4,922,974원 × 5%</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>6-1-4 p186</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>공사 규모 판정</t>
+          <t>적용 기준</t>
         </is>
       </c>
       <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="14" t="inlineStr">
-        <is>
-          <t>전체 공사 규모: 이 견적만 기준(5,650,840원)으로 제비율 구간을 선택했습니다.</t>
-        </is>
-      </c>
+      <c r="C22" s="14" t="inlineStr"/>
       <c r="D22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>안전관리비 기초액</t>
+          <t>공사 규모 판정</t>
         </is>
       </c>
       <c r="B23" s="20" t="inlineStr"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
+          <t>전체 공사 규모: 이 견적만 기준(5,650,840원)으로 제비율 구간을 선택했습니다.</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>안전관리비 기초액</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="14" t="inlineStr">
+        <is>
           <t>산업안전보건관리비 기초액은 전체 공사에 1회 계상 — 부분 견적에서 제외(간이).</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr"/>
-    </row>
-    <row r="24" ht="23" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="D24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25" ht="23" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>표준품셈 기준 금액 · 검토 전 참고용 · 품셈AI</t>
         </is>
       </c>
-      <c r="B24" s="20" t="n"/>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="14" t="n"/>
+      <c r="B25" s="20" t="n"/>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
